--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$3</f>
+              <f>'Equity-Kurve'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$3</f>
+              <f>'Equity-Kurve'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 06:24 UTC</t>
+          <t>2026-05-26 07:11 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,16 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>5000</v>
       </c>
     </row>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$4</f>
+              <f>'Equity-Kurve'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$4</f>
+              <f>'Equity-Kurve'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 07:11 UTC</t>
+          <t>2026-05-26 23:06 UTC</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,16 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -935,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -981,7 +991,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aktuell keine offenen Positionen.</t>
+          <t>Tranche_2x</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>USD/JPY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>159.2519989013672</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>USD/JPY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>159.2519989013672</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10 %</t>
         </is>
       </c>
     </row>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$5</f>
+              <f>'Equity-Kurve'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$5</f>
+              <f>'Equity-Kurve'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 23:06 UTC</t>
+          <t>2026-05-27 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5000.00 CHF</t>
+          <t>4994.37 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.00 %</t>
+          <t>-0.11 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+0.00 %</t>
+          <t>-5.52 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>+0.00 %</t>
+          <t>-0.11 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -931,6 +931,16 @@
       </c>
       <c r="B5" t="n">
         <v>5000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4994.37</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$6</f>
+              <f>'Equity-Kurve'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$6</f>
+              <f>'Equity-Kurve'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27 23:14 UTC</t>
+          <t>2026-05-28 23:12 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4994.37 CHF</t>
+          <t>5000.20 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.11 %</t>
+          <t>+0.00 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-5.52 %</t>
+          <t>+0.17 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -941,6 +941,16 @@
       </c>
       <c r="B6" t="n">
         <v>4994.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5000.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$7</f>
+              <f>'Equity-Kurve'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$7</f>
+              <f>'Equity-Kurve'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28 23:12 UTC</t>
+          <t>2026-05-29 23:09 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5000.20 CHF</t>
+          <t>4999.93 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.00 %</t>
+          <t>-0.00 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+0.17 %</t>
+          <t>-0.05 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -951,6 +951,16 @@
       </c>
       <c r="B7" t="n">
         <v>5000.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4999.93</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$8</f>
+              <f>'Equity-Kurve'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$8</f>
+              <f>'Equity-Kurve'!$B$2:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29 23:09 UTC</t>
+          <t>2026-06-01 23:25 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4999.93 CHF</t>
+          <t>4991.16 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.00 %</t>
+          <t>-0.18 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.05 %</t>
+          <t>-5.42 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.11 %</t>
+          <t>-0.18 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,16 @@
       </c>
       <c r="B8" t="n">
         <v>4999.93</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4991.16</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$9</f>
+              <f>'Equity-Kurve'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$9</f>
+              <f>'Equity-Kurve'!$B$2:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01 23:25 UTC</t>
+          <t>2026-06-02 23:43 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4991.16 CHF</t>
+          <t>4983.63 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.18 %</t>
+          <t>-0.33 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-5.42 %</t>
+          <t>-8.77 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.18 %</t>
+          <t>-0.33 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -971,6 +971,16 @@
       </c>
       <c r="B9" t="n">
         <v>4991.16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4983.63</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$10</f>
+              <f>'Equity-Kurve'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$10</f>
+              <f>'Equity-Kurve'!$B$2:$B$11</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-02 23:43 UTC</t>
+          <t>2026-06-03 23:29 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4983.63 CHF</t>
+          <t>4984.38 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.33 %</t>
+          <t>-0.31 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-8.77 %</t>
+          <t>-7.58 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,16 @@
       </c>
       <c r="B10" t="n">
         <v>4983.63</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4984.38</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1071,28 +1081,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Tranche_2x</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>USD/CHF</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7914599776268005</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Tranche_15x</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>USD/JPY</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>159.2519989013672</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>USD/CHF</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7914599776268005</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>10 %</t>
         </is>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$11</f>
+              <f>'Equity-Kurve'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$11</f>
+              <f>'Equity-Kurve'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-03 23:29 UTC</t>
+          <t>2026-06-04 23:06 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4984.38 CHF</t>
+          <t>4992.87 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.31 %</t>
+          <t>-0.14 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-7.58 %</t>
+          <t>-3.22 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -991,6 +991,16 @@
       </c>
       <c r="B11" t="n">
         <v>4984.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4992.87</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$12</f>
+              <f>'Equity-Kurve'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$12</f>
+              <f>'Equity-Kurve'!$B$2:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04 23:06 UTC</t>
+          <t>2026-06-05 23:04 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4992.87 CHF</t>
+          <t>4954.91 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.14 %</t>
+          <t>-0.90 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.22 %</t>
+          <t>-17.32 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.33 %</t>
+          <t>-0.91 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1001,6 +1001,16 @@
       </c>
       <c r="B12" t="n">
         <v>4992.87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4954.91</v>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1121,26 +1131,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tranche_15x</t>
+          <t>Tranche_2x</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>159.2519989013672</v>
+        <v>1.152737736701965</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1151,28 +1161,208 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Tranche_2x</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GBP/USD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.333617806434631</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tranche_2x</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AUD/USD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7049700617790222</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Tranche_15x</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>USD/JPY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SHORT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>159.2519989013672</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>USD/CHF</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>SHORT</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E8" t="n">
         <v>0.7914599776268005</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EUR/USD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1.152737736701965</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GBP/USD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1.333617806434631</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tranche_15x</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AUD/USD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LONG</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7049700617790222</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>10 %</t>
         </is>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$13</f>
+              <f>'Equity-Kurve'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$13</f>
+              <f>'Equity-Kurve'!$B$2:$B$14</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-05 23:04 UTC</t>
+          <t>2026-06-08 23:10 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4954.91 CHF</t>
+          <t>4954.54 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.90 %</t>
+          <t>-0.91 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-17.32 %</t>
+          <t>-16.23 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1011,6 +1011,16 @@
       </c>
       <c r="B13" t="n">
         <v>4954.91</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4954.54</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$14</f>
+              <f>'Equity-Kurve'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$14</f>
+              <f>'Equity-Kurve'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:10 UTC</t>
+          <t>2026-06-09 23:15 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4954.54 CHF</t>
+          <t>4941.15 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.91 %</t>
+          <t>-1.18 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-16.23 %</t>
+          <t>-19.19 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-0.91 %</t>
+          <t>-1.18 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1021,6 +1021,16 @@
       </c>
       <c r="B14" t="n">
         <v>4954.54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4941.15</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$15</f>
+              <f>'Equity-Kurve'!$A$2:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$15</f>
+              <f>'Equity-Kurve'!$B$2:$B$16</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-09 23:15 UTC</t>
+          <t>2026-06-10 23:23 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4941.15 CHF</t>
+          <t>4911.66 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.18 %</t>
+          <t>-1.77 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-19.19 %</t>
+          <t>-25.88 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-1.18 %</t>
+          <t>-1.77 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1031,6 +1031,16 @@
       </c>
       <c r="B15" t="n">
         <v>4941.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4911.66</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$16</f>
+              <f>'Equity-Kurve'!$A$2:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$16</f>
+              <f>'Equity-Kurve'!$B$2:$B$17</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-10 23:23 UTC</t>
+          <t>2026-06-11 23:19 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4911.66 CHF</t>
+          <t>5010.33 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.77 %</t>
+          <t>+0.21 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-25.88 %</t>
+          <t>+3.30 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1041,6 +1041,16 @@
       </c>
       <c r="B16" t="n">
         <v>4911.66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5010.33</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$17</f>
+              <f>'Equity-Kurve'!$A$2:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$17</f>
+              <f>'Equity-Kurve'!$B$2:$B$18</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-11 23:19 UTC</t>
+          <t>2026-06-12 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5010.33 CHF</t>
+          <t>4989.31 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.21 %</t>
+          <t>-0.21 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+3.30 %</t>
+          <t>-3.12 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1051,6 +1051,16 @@
       </c>
       <c r="B17" t="n">
         <v>5010.33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4989.31</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$18</f>
+              <f>'Equity-Kurve'!$A$2:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$18</f>
+              <f>'Equity-Kurve'!$B$2:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-12 23:14 UTC</t>
+          <t>2026-06-15 23:43 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4989.31 CHF</t>
+          <t>5017.91 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.21 %</t>
+          <t>+0.36 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.12 %</t>
+          <t>+5.13 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1061,6 +1061,16 @@
       </c>
       <c r="B18" t="n">
         <v>4989.31</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5017.91</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$19</f>
+              <f>'Equity-Kurve'!$A$2:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$19</f>
+              <f>'Equity-Kurve'!$B$2:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15 23:43 UTC</t>
+          <t>2026-06-16 23:21 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5017.91 CHF</t>
+          <t>5032.95 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.36 %</t>
+          <t>+0.66 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+5.13 %</t>
+          <t>+9.10 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1071,6 +1071,16 @@
       </c>
       <c r="B19" t="n">
         <v>5017.91</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5032.95</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$20</f>
+              <f>'Equity-Kurve'!$A$2:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$20</f>
+              <f>'Equity-Kurve'!$B$2:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-16 23:21 UTC</t>
+          <t>2026-06-17 23:20 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5032.95 CHF</t>
+          <t>4905.00 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.66 %</t>
+          <t>-1.90 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+9.10 %</t>
+          <t>-21.47 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-1.77 %</t>
+          <t>-2.54 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1081,16 @@
       </c>
       <c r="B20" t="n">
         <v>5032.95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4905</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$21</f>
+              <f>'Equity-Kurve'!$A$2:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$21</f>
+              <f>'Equity-Kurve'!$B$2:$B$22</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-17 23:20 UTC</t>
+          <t>2026-06-18 23:42 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4905.00 CHF</t>
+          <t>4823.54 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.90 %</t>
+          <t>-3.53 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-21.47 %</t>
+          <t>-35.02 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-2.54 %</t>
+          <t>-4.16 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1091,6 +1091,16 @@
       </c>
       <c r="B21" t="n">
         <v>4905</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4823.54</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$22</f>
+              <f>'Equity-Kurve'!$A$2:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$22</f>
+              <f>'Equity-Kurve'!$B$2:$B$23</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18 23:42 UTC</t>
+          <t>2026-06-19 22:52 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4823.54 CHF</t>
+          <t>4823.87 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.53 %</t>
+          <t>-3.52 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-35.02 %</t>
+          <t>-33.69 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1101,6 +1101,16 @@
       </c>
       <c r="B22" t="n">
         <v>4823.54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4823.87</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$23</f>
+              <f>'Equity-Kurve'!$A$2:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$23</f>
+              <f>'Equity-Kurve'!$B$2:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-19 22:52 UTC</t>
+          <t>2026-06-22 23:16 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4823.87 CHF</t>
+          <t>4789.92 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.52 %</t>
+          <t>-4.20 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-33.69 %</t>
+          <t>-37.52 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-4.16 %</t>
+          <t>-4.83 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1111,16 @@
       </c>
       <c r="B23" t="n">
         <v>4823.87</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4789.92</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$24</f>
+              <f>'Equity-Kurve'!$A$2:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$24</f>
+              <f>'Equity-Kurve'!$B$2:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-22 23:16 UTC</t>
+          <t>2026-06-23 23:05 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4789.92 CHF</t>
+          <t>4718.89 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.20 %</t>
+          <t>-5.62 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-37.52 %</t>
+          <t>-45.53 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-4.83 %</t>
+          <t>-6.24 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,16 @@
       </c>
       <c r="B24" t="n">
         <v>4789.92</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4718.89</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$25</f>
+              <f>'Equity-Kurve'!$A$2:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$25</f>
+              <f>'Equity-Kurve'!$B$2:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-23 23:05 UTC</t>
+          <t>2026-06-24 23:01 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4718.89 CHF</t>
+          <t>4671.70 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.62 %</t>
+          <t>-6.57 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-45.53 %</t>
+          <t>-49.57 %</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-6.24 %</t>
+          <t>-7.18 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1131,16 @@
       </c>
       <c r="B25" t="n">
         <v>4718.89</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4671.7</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$26</f>
+              <f>'Equity-Kurve'!$A$2:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$26</f>
+              <f>'Equity-Kurve'!$B$2:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-24 23:01 UTC</t>
+          <t>2026-06-25 23:14 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4671.70 CHF</t>
+          <t>4696.44 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.57 %</t>
+          <t>-6.07 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-49.57 %</t>
+          <t>-45.50 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1141,6 +1141,16 @@
       </c>
       <c r="B26" t="n">
         <v>4671.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4696.44</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$27</f>
+              <f>'Equity-Kurve'!$A$2:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$27</f>
+              <f>'Equity-Kurve'!$B$2:$B$28</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-25 23:14 UTC</t>
+          <t>2026-06-26 23:02 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4696.44 CHF</t>
+          <t>4705.76 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.07 %</t>
+          <t>-5.88 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-45.50 %</t>
+          <t>-43.22 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1151,6 +1151,16 @@
       </c>
       <c r="B27" t="n">
         <v>4696.44</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4705.76</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$28</f>
+              <f>'Equity-Kurve'!$A$2:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$28</f>
+              <f>'Equity-Kurve'!$B$2:$B$29</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-26 23:02 UTC</t>
+          <t>2026-06-29 22:53 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4705.76 CHF</t>
+          <t>4722.07 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.88 %</t>
+          <t>-5.56 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-43.22 %</t>
+          <t>-40.23 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1161,6 +1161,16 @@
       </c>
       <c r="B28" t="n">
         <v>4705.76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4722.07</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$29</f>
+              <f>'Equity-Kurve'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$29</f>
+              <f>'Equity-Kurve'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-29 22:53 UTC</t>
+          <t>2026-06-30 23:07 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4722.07 CHF</t>
+          <t>4727.83 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.56 %</t>
+          <t>-5.44 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-40.23 %</t>
+          <t>-38.51 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1171,6 +1171,16 @@
       </c>
       <c r="B29" t="n">
         <v>4722.07</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4727.83</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$30</f>
+              <f>'Equity-Kurve'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$30</f>
+              <f>'Equity-Kurve'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30 23:07 UTC</t>
+          <t>2026-07-01 23:10 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4727.83 CHF</t>
+          <t>4704.39 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.44 %</t>
+          <t>-5.91 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-38.51 %</t>
+          <t>-40.07 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,16 @@
       </c>
       <c r="B30" t="n">
         <v>4727.83</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4704.39</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$31</f>
+              <f>'Equity-Kurve'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$31</f>
+              <f>'Equity-Kurve'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01 23:10 UTC</t>
+          <t>2026-07-02 23:00 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4704.39 CHF</t>
+          <t>4790.83 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.91 %</t>
+          <t>-4.18 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-40.07 %</t>
+          <t>-29.35 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1191,6 +1191,16 @@
       </c>
       <c r="B31" t="n">
         <v>4704.39</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4790.83</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$32</f>
+              <f>'Equity-Kurve'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$32</f>
+              <f>'Equity-Kurve'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-02 23:00 UTC</t>
+          <t>2026-07-03 22:58 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4790.83 CHF</t>
+          <t>4823.82 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.18 %</t>
+          <t>-3.52 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-29.35 %</t>
+          <t>-24.61 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1201,6 +1201,16 @@
       </c>
       <c r="B32" t="n">
         <v>4790.83</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4823.82</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$33</f>
+              <f>'Equity-Kurve'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$33</f>
+              <f>'Equity-Kurve'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-03 22:58 UTC</t>
+          <t>2026-07-06 23:03 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4823.82 CHF</t>
+          <t>4825.46 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.52 %</t>
+          <t>-3.49 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-24.61 %</t>
+          <t>-23.76 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1211,6 +1211,16 @@
       </c>
       <c r="B33" t="n">
         <v>4823.82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4825.46</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$34</f>
+              <f>'Equity-Kurve'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$34</f>
+              <f>'Equity-Kurve'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-06 23:03 UTC</t>
+          <t>2026-07-07 22:57 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4825.46 CHF</t>
+          <t>4763.30 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.49 %</t>
+          <t>-4.73 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-23.76 %</t>
+          <t>-30.19 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1221,6 +1221,16 @@
       </c>
       <c r="B34" t="n">
         <v>4825.46</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4763.3</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$35</f>
+              <f>'Equity-Kurve'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$35</f>
+              <f>'Equity-Kurve'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-07 22:57 UTC</t>
+          <t>2026-07-08 23:01 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4763.30 CHF</t>
+          <t>4771.97 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.73 %</t>
+          <t>-4.56 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-30.19 %</t>
+          <t>-28.54 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1231,6 +1231,16 @@
       </c>
       <c r="B35" t="n">
         <v>4763.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4771.97</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$36</f>
+              <f>'Equity-Kurve'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$36</f>
+              <f>'Equity-Kurve'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08 23:01 UTC</t>
+          <t>2026-07-09 23:08 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4771.97 CHF</t>
+          <t>4800.75 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.56 %</t>
+          <t>-3.99 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-28.54 %</t>
+          <t>-24.77 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1241,6 +1241,16 @@
       </c>
       <c r="B36" t="n">
         <v>4771.97</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4800.75</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$37</f>
+              <f>'Equity-Kurve'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$37</f>
+              <f>'Equity-Kurve'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-09 23:08 UTC</t>
+          <t>2026-07-10 22:56 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4800.75 CHF</t>
+          <t>4805.67 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.99 %</t>
+          <t>-3.89 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-24.77 %</t>
+          <t>-23.66 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1251,16 @@
       </c>
       <c r="B37" t="n">
         <v>4800.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4805.67</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$38</f>
+              <f>'Equity-Kurve'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$38</f>
+              <f>'Equity-Kurve'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-10 22:56 UTC</t>
+          <t>2026-07-13 22:52 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4805.67 CHF</t>
+          <t>4715.80 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.89 %</t>
+          <t>-5.68 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-23.66 %</t>
+          <t>-32.16 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1261,16 @@
       </c>
       <c r="B38" t="n">
         <v>4805.67</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4715.8</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$39</f>
+              <f>'Equity-Kurve'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$39</f>
+              <f>'Equity-Kurve'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-13 22:52 UTC</t>
+          <t>2026-07-14 22:54 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4715.80 CHF</t>
+          <t>4795.82 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-5.68 %</t>
+          <t>-4.08 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-32.16 %</t>
+          <t>-23.62 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1271,6 +1271,16 @@
       </c>
       <c r="B39" t="n">
         <v>4715.8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4795.82</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$40</f>
+              <f>'Equity-Kurve'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$40</f>
+              <f>'Equity-Kurve'!$B$2:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-14 22:54 UTC</t>
+          <t>2026-07-15 22:55 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4795.82 CHF</t>
+          <t>4888.37 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.08 %</t>
+          <t>-2.23 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-23.62 %</t>
+          <t>-13.26 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1281,6 +1281,16 @@
       </c>
       <c r="B40" t="n">
         <v>4795.82</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4888.37</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$41</f>
+              <f>'Equity-Kurve'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$41</f>
+              <f>'Equity-Kurve'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-15 22:55 UTC</t>
+          <t>2026-07-16 22:54 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4888.37 CHF</t>
+          <t>4836.57 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-2.23 %</t>
+          <t>-3.27 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-13.26 %</t>
+          <t>-18.47 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1291,6 +1291,16 @@
       </c>
       <c r="B41" t="n">
         <v>4888.37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4836.57</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$42</f>
+              <f>'Equity-Kurve'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$42</f>
+              <f>'Equity-Kurve'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16 22:54 UTC</t>
+          <t>2026-07-17 22:44 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4836.57 CHF</t>
+          <t>4832.13 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.27 %</t>
+          <t>-3.36 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-18.47 %</t>
+          <t>-18.53 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1301,6 +1301,16 @@
       </c>
       <c r="B42" t="n">
         <v>4836.57</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>4832.13</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$43</f>
+              <f>'Equity-Kurve'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$43</f>
+              <f>'Equity-Kurve'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-17 22:44 UTC</t>
+          <t>2026-07-20 22:55 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4832.13 CHF</t>
+          <t>4805.14 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.36 %</t>
+          <t>-3.90 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-18.53 %</t>
+          <t>-20.78 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1311,6 +1311,16 @@
       </c>
       <c r="B43" t="n">
         <v>4832.13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4805.14</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$44</f>
+              <f>'Equity-Kurve'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$44</f>
+              <f>'Equity-Kurve'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20 22:55 UTC</t>
+          <t>2026-07-21 22:51 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4805.14 CHF</t>
+          <t>4760.12 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-3.90 %</t>
+          <t>-4.80 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-20.78 %</t>
+          <t>-24.54 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1321,6 +1321,16 @@
       </c>
       <c r="B44" t="n">
         <v>4805.14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4760.12</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$45</f>
+              <f>'Equity-Kurve'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$45</f>
+              <f>'Equity-Kurve'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-21 22:51 UTC</t>
+          <t>2026-07-22 22:57 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4760.12 CHF</t>
+          <t>4750.94 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.80 %</t>
+          <t>-4.98 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-24.54 %</t>
+          <t>-24.88 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1331,6 +1331,16 @@
       </c>
       <c r="B45" t="n">
         <v>4760.12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4750.94</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$46</f>
+              <f>'Equity-Kurve'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$46</f>
+              <f>'Equity-Kurve'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-22 22:57 UTC</t>
+          <t>2026-07-23 22:52 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4750.94 CHF</t>
+          <t>4690.92 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.98 %</t>
+          <t>-6.18 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-24.88 %</t>
+          <t>-29.50 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1341,6 +1341,16 @@
       </c>
       <c r="B46" t="n">
         <v>4750.94</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>4690.92</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$47</f>
+              <f>'Equity-Kurve'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$47</f>
+              <f>'Equity-Kurve'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-23 22:52 UTC</t>
+          <t>2026-07-24 22:57 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4690.92 CHF</t>
+          <t>4691.85 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.18 %</t>
+          <t>-6.16 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-29.50 %</t>
+          <t>-28.90 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1351,6 +1351,16 @@
       </c>
       <c r="B47" t="n">
         <v>4690.92</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4691.85</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$48</f>
+              <f>'Equity-Kurve'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$48</f>
+              <f>'Equity-Kurve'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-24 22:57 UTC</t>
+          <t>2026-07-27 22:57 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4691.85 CHF</t>
+          <t>4680.71 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.16 %</t>
+          <t>-6.39 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-28.90 %</t>
+          <t>-29.28 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1361,6 +1361,16 @@
       </c>
       <c r="B48" t="n">
         <v>4691.85</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4680.71</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$49</f>
+              <f>'Equity-Kurve'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$49</f>
+              <f>'Equity-Kurve'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27 22:57 UTC</t>
+          <t>2026-07-28 22:54 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4680.71 CHF</t>
+          <t>4673.18 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.39 %</t>
+          <t>-6.54 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-29.28 %</t>
+          <t>-29.37 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1371,6 +1371,16 @@
       </c>
       <c r="B49" t="n">
         <v>4680.71</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4673.18</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$50</f>
+              <f>'Equity-Kurve'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$50</f>
+              <f>'Equity-Kurve'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-28 22:54 UTC</t>
+          <t>2026-07-29 22:56 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4673.18 CHF</t>
+          <t>4751.63 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-6.54 %</t>
+          <t>-4.97 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-29.37 %</t>
+          <t>-22.65 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1381,6 +1381,16 @@
       </c>
       <c r="B50" t="n">
         <v>4673.18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4751.63</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$51</f>
+              <f>'Equity-Kurve'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$51</f>
+              <f>'Equity-Kurve'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-29 22:56 UTC</t>
+          <t>2026-07-30 23:01 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4751.63 CHF</t>
+          <t>4959.40 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-4.97 %</t>
+          <t>-0.81 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-22.65 %</t>
+          <t>-3.95 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1391,6 +1391,16 @@
       </c>
       <c r="B51" t="n">
         <v>4751.63</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4959.4</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$52</f>
+              <f>'Equity-Kurve'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$52</f>
+              <f>'Equity-Kurve'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-30 23:01 UTC</t>
+          <t>2026-07-31 22:55 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4959.40 CHF</t>
+          <t>4997.61 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.81 %</t>
+          <t>-0.05 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.95 %</t>
+          <t>-0.23 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1401,16 @@
       </c>
       <c r="B52" t="n">
         <v>4959.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4997.61</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$53</f>
+              <f>'Equity-Kurve'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$53</f>
+              <f>'Equity-Kurve'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31 22:55 UTC</t>
+          <t>2026-08-03 22:56 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4997.61 CHF</t>
+          <t>4954.15 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.05 %</t>
+          <t>-0.92 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.23 %</t>
+          <t>-4.29 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1411,6 +1411,16 @@
       </c>
       <c r="B53" t="n">
         <v>4997.61</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>4954.15</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$54</f>
+              <f>'Equity-Kurve'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$54</f>
+              <f>'Equity-Kurve'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-03 22:56 UTC</t>
+          <t>2026-08-04 22:58 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4954.15 CHF</t>
+          <t>4988.55 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.92 %</t>
+          <t>-0.23 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.29 %</t>
+          <t>-1.06 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1421,6 +1421,16 @@
       </c>
       <c r="B54" t="n">
         <v>4954.15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>4988.55</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$55</f>
+              <f>'Equity-Kurve'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$55</f>
+              <f>'Equity-Kurve'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04 22:58 UTC</t>
+          <t>2026-08-05 22:54 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4988.55 CHF</t>
+          <t>5014.61 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.23 %</t>
+          <t>+0.29 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.06 %</t>
+          <t>+1.35 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1431,16 @@
       </c>
       <c r="B55" t="n">
         <v>4988.55</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5014.61</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$56</f>
+              <f>'Equity-Kurve'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$56</f>
+              <f>'Equity-Kurve'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-05 22:54 UTC</t>
+          <t>2026-08-07 01:29 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5014.61 CHF</t>
+          <t>4944.07 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.29 %</t>
+          <t>-1.12 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+1.35 %</t>
+          <t>-4.94 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1441,6 +1441,16 @@
       </c>
       <c r="B56" t="n">
         <v>5014.61</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4944.07</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$57</f>
+              <f>'Equity-Kurve'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$57</f>
+              <f>'Equity-Kurve'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07 01:29 UTC</t>
+          <t>2026-08-07 22:30 UTC</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4944.07 CHF</t>
+          <t>5024.11 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.12 %</t>
+          <t>+0.48 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.94 %</t>
+          <t>+2.15 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1451,16 @@
       </c>
       <c r="B57" t="n">
         <v>4944.07</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5024.11</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$58</f>
+              <f>'Equity-Kurve'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$58</f>
+              <f>'Equity-Kurve'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-07 22:30 UTC</t>
+          <t>2026-08-10 22:32 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5024.11 CHF</t>
+          <t>4969.98 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.48 %</t>
+          <t>-0.60 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+2.15 %</t>
+          <t>-2.58 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1461,6 +1461,16 @@
       </c>
       <c r="B58" t="n">
         <v>5024.11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>4969.98</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$59</f>
+              <f>'Equity-Kurve'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$59</f>
+              <f>'Equity-Kurve'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-10 22:32 UTC</t>
+          <t>2026-08-11 22:36 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4969.98 CHF</t>
+          <t>4971.74 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.60 %</t>
+          <t>-0.57 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-2.58 %</t>
+          <t>-2.39 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1471,6 +1471,16 @@
       </c>
       <c r="B59" t="n">
         <v>4969.98</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4971.74</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$60</f>
+              <f>'Equity-Kurve'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$60</f>
+              <f>'Equity-Kurve'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-11 22:36 UTC</t>
+          <t>2026-08-12 22:35 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4971.74 CHF</t>
+          <t>4957.58 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.57 %</t>
+          <t>-0.85 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-2.39 %</t>
+          <t>-3.52 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1481,6 +1481,16 @@
       </c>
       <c r="B60" t="n">
         <v>4971.74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4957.58</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Trades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Equity-Kurve" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Offene Positionen" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity-Kurve" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene Positionen" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,13 +153,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -182,26 +182,26 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$61</f>
+              <f>'Equity-Kurve'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$61</f>
+              <f>'Equity-Kurve'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -217,8 +217,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -244,8 +244,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -271,7 +271,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -286,9 +286,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12 22:35 UTC</t>
+          <t>2026-08-13 22:36 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4957.58 CHF</t>
+          <t>4941.24 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.85 %</t>
+          <t>-1.18 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-3.52 %</t>
+          <t>-4.77 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1491,6 +1491,16 @@
       </c>
       <c r="B61" t="n">
         <v>4957.58</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4941.24</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$62</f>
+              <f>'Equity-Kurve'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$62</f>
+              <f>'Equity-Kurve'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-13 22:36 UTC</t>
+          <t>2026-08-14 22:18 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4941.24 CHF</t>
+          <t>4987.76 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-1.18 %</t>
+          <t>-0.24 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-4.77 %</t>
+          <t>-0.99 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1501,6 +1501,16 @@
       </c>
       <c r="B62" t="n">
         <v>4941.24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4987.76</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$63</f>
+              <f>'Equity-Kurve'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$63</f>
+              <f>'Equity-Kurve'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14 22:18 UTC</t>
+          <t>2026-08-17 22:19 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4987.76 CHF</t>
+          <t>5008.59 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.24 %</t>
+          <t>+0.17 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.99 %</t>
+          <t>+0.69 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1511,6 +1511,16 @@
       </c>
       <c r="B63" t="n">
         <v>4987.76</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5008.59</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$64</f>
+              <f>'Equity-Kurve'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$64</f>
+              <f>'Equity-Kurve'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17 22:19 UTC</t>
+          <t>2026-08-18 22:18 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5008.59 CHF</t>
+          <t>4985.49 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.17 %</t>
+          <t>-0.29 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+0.69 %</t>
+          <t>-1.14 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1521,6 +1521,16 @@
       </c>
       <c r="B64" t="n">
         <v>5008.59</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>4985.49</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$65</f>
+              <f>'Equity-Kurve'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$65</f>
+              <f>'Equity-Kurve'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-18 22:18 UTC</t>
+          <t>2026-08-19 22:19 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4985.49 CHF</t>
+          <t>5162.03 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.29 %</t>
+          <t>+3.24 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-1.14 %</t>
+          <t>+13.16 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1531,6 +1531,16 @@
       </c>
       <c r="B65" t="n">
         <v>4985.49</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5162.03</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$66</f>
+              <f>'Equity-Kurve'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$66</f>
+              <f>'Equity-Kurve'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-19 22:19 UTC</t>
+          <t>2026-08-20 22:21 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5162.03 CHF</t>
+          <t>5129.48 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3.24 %</t>
+          <t>+2.59 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+13.16 %</t>
+          <t>+10.25 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1541,16 @@
       </c>
       <c r="B66" t="n">
         <v>5162.03</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5129.48</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$67</f>
+              <f>'Equity-Kurve'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$67</f>
+              <f>'Equity-Kurve'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-20 22:21 UTC</t>
+          <t>2026-08-21 22:18 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5129.48 CHF</t>
+          <t>5161.20 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.59 %</t>
+          <t>+3.22 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+10.25 %</t>
+          <t>+12.68 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1551,6 +1551,16 @@
       </c>
       <c r="B67" t="n">
         <v>5129.48</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5161.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$68</f>
+              <f>'Equity-Kurve'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$68</f>
+              <f>'Equity-Kurve'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 22:18 UTC</t>
+          <t>2026-08-24 22:20 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5161.20 CHF</t>
+          <t>5130.23 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3.22 %</t>
+          <t>+2.60 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+12.68 %</t>
+          <t>+10.00 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1561,6 +1561,16 @@
       </c>
       <c r="B68" t="n">
         <v>5161.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>5130.23</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$69</f>
+              <f>'Equity-Kurve'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$69</f>
+              <f>'Equity-Kurve'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 22:20 UTC</t>
+          <t>2026-08-25 22:21 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5130.23 CHF</t>
+          <t>5147.68 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.60 %</t>
+          <t>+2.95 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+10.00 %</t>
+          <t>+11.22 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1571,6 +1571,16 @@
       </c>
       <c r="B69" t="n">
         <v>5130.23</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5147.68</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$70</f>
+              <f>'Equity-Kurve'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$70</f>
+              <f>'Equity-Kurve'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-25 22:21 UTC</t>
+          <t>2026-08-27 02:50 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5147.68 CHF</t>
+          <t>5114.93 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.95 %</t>
+          <t>+2.30 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+11.22 %</t>
+          <t>+8.53 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1581,6 +1581,16 @@
       </c>
       <c r="B70" t="n">
         <v>5147.68</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5114.93</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$71</f>
+              <f>'Equity-Kurve'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$71</f>
+              <f>'Equity-Kurve'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-27 02:50 UTC</t>
+          <t>2026-08-28 05:55 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5114.93 CHF</t>
+          <t>5113.45 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.30 %</t>
+          <t>+2.27 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+8.53 %</t>
+          <t>+8.29 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1591,6 +1591,16 @@
       </c>
       <c r="B71" t="n">
         <v>5114.93</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5113.45</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$72</f>
+              <f>'Equity-Kurve'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$72</f>
+              <f>'Equity-Kurve'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 05:55 UTC</t>
+          <t>2026-08-29 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5113.45 CHF</t>
+          <t>5032.74 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.27 %</t>
+          <t>+0.65 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+8.29 %</t>
+          <t>+2.31 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1601,6 +1601,16 @@
       </c>
       <c r="B72" t="n">
         <v>5113.45</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5032.74</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$73</f>
+              <f>'Equity-Kurve'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$73</f>
+              <f>'Equity-Kurve'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29 03:27 UTC</t>
+          <t>2026-09-01 00:57 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5032.74 CHF</t>
+          <t>5061.81 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.65 %</t>
+          <t>+1.24 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+2.31 %</t>
+          <t>+4.33 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1611,6 +1611,16 @@
       </c>
       <c r="B73" t="n">
         <v>5032.74</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>5061.81</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$74</f>
+              <f>'Equity-Kurve'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$74</f>
+              <f>'Equity-Kurve'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 00:57 UTC</t>
+          <t>2026-09-01 23:44 UTC</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5061.81 CHF</t>
+          <t>5007.79 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+1.24 %</t>
+          <t>+0.16 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+4.33 %</t>
+          <t>+0.53 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1621,6 +1621,16 @@
       </c>
       <c r="B74" t="n">
         <v>5061.81</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5007.79</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$75</f>
+              <f>'Equity-Kurve'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$75</f>
+              <f>'Equity-Kurve'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 23:44 UTC</t>
+          <t>2026-09-02 23:48 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5007.79 CHF</t>
+          <t>5029.57 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.16 %</t>
+          <t>+0.59 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+0.53 %</t>
+          <t>+2.00 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1631,6 +1631,16 @@
       </c>
       <c r="B75" t="n">
         <v>5007.79</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>5029.57</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$76</f>
+              <f>'Equity-Kurve'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$76</f>
+              <f>'Equity-Kurve'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 23:48 UTC</t>
+          <t>2026-09-03 23:45 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5029.57 CHF</t>
+          <t>5165.09 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+0.59 %</t>
+          <t>+3.30 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+2.00 %</t>
+          <t>+11.37 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1641,6 +1641,16 @@
       </c>
       <c r="B76" t="n">
         <v>5029.57</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>5165.09</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$77</f>
+              <f>'Equity-Kurve'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$77</f>
+              <f>'Equity-Kurve'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 23:45 UTC</t>
+          <t>2026-09-04 23:39 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5165.09 CHF</t>
+          <t>5146.20 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+3.30 %</t>
+          <t>+2.92 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+11.37 %</t>
+          <t>+9.89 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1651,6 +1651,16 @@
       </c>
       <c r="B77" t="n">
         <v>5165.09</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>5146.2</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$78</f>
+              <f>'Equity-Kurve'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$78</f>
+              <f>'Equity-Kurve'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04 23:39 UTC</t>
+          <t>2026-09-07 23:55 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5146.20 CHF</t>
+          <t>5218.21 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.92 %</t>
+          <t>+4.36 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+9.89 %</t>
+          <t>+14.80 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1661,6 +1661,16 @@
       </c>
       <c r="B78" t="n">
         <v>5146.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5218.21</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$79</f>
+              <f>'Equity-Kurve'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$79</f>
+              <f>'Equity-Kurve'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07 23:55 UTC</t>
+          <t>2026-09-08 23:48 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5218.21 CHF</t>
+          <t>5229.47 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+4.36 %</t>
+          <t>+4.59 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+14.80 %</t>
+          <t>+15.39 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1671,6 +1671,16 @@
       </c>
       <c r="B79" t="n">
         <v>5218.21</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>5229.47</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$80</f>
+              <f>'Equity-Kurve'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$80</f>
+              <f>'Equity-Kurve'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 23:48 UTC</t>
+          <t>2026-09-09 23:47 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5229.47 CHF</t>
+          <t>5229.39 CHF</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+15.39 %</t>
+          <t>+15.18 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,16 @@
       </c>
       <c r="B80" t="n">
         <v>5229.47</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>5229.39</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$81</f>
+              <f>'Equity-Kurve'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$81</f>
+              <f>'Equity-Kurve'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 23:47 UTC</t>
+          <t>2026-09-10 23:39 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5229.39 CHF</t>
+          <t>5137.81 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+4.59 %</t>
+          <t>+2.76 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+15.18 %</t>
+          <t>+8.83 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1691,6 +1691,16 @@
       </c>
       <c r="B81" t="n">
         <v>5229.39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>5137.81</v>
       </c>
     </row>
   </sheetData>

--- a/results/paper_report.xlsx
+++ b/results/paper_report.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Equity-Kurve'!$A$2:$A$82</f>
+              <f>'Equity-Kurve'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Equity-Kurve'!$B$2:$B$82</f>
+              <f>'Equity-Kurve'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -611,7 +611,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-10 23:39 UTC</t>
+          <t>2026-09-11 23:50 UTC</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5137.81 CHF</t>
+          <t>5154.88 CHF</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>+2.76 %</t>
+          <t>+3.10 %</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+8.83 %</t>
+          <t>+9.83 %</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1701,16 @@
       </c>
       <c r="B82" t="n">
         <v>5137.81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>5154.88</v>
       </c>
     </row>
   </sheetData>
